--- a/NFLX.xlsx
+++ b/NFLX.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29530"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Martin Shkreli\code\models\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Martin Shkreli - DL\models\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F7DB7B46-734D-4272-ABE1-618C0B8A120A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C177FE7F-6CCA-4014-BA5A-32D2B3D96008}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="220" yWindow="240" windowWidth="23430" windowHeight="20070" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="8410" yWindow="310" windowWidth="29080" windowHeight="15460" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="8" r:id="rId1"/>
@@ -1083,7 +1083,7 @@
     <xf numFmtId="37" fontId="12" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="139">
+  <cellXfs count="138">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="3" applyFont="1"/>
@@ -1288,6 +1288,7 @@
     <xf numFmtId="3" fontId="15" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="4" fontId="6" fillId="0" borderId="0" xfId="5" applyNumberFormat="1"/>
     <xf numFmtId="167" fontId="14" fillId="0" borderId="0" xfId="4" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1305,8 +1306,6 @@
     <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="5" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="3" fontId="6" fillId="0" borderId="0" xfId="5" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="4" fontId="6" fillId="0" borderId="0" xfId="5" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="9">
     <cellStyle name="Comma" xfId="1" builtinId="3"/>
@@ -5012,7 +5011,8 @@
         <v>105</v>
       </c>
       <c r="N3" s="92">
-        <v>434</v>
+        <f>434*10</f>
+        <v>4340</v>
       </c>
       <c r="O3" s="90" t="s">
         <v>132</v>
@@ -5024,7 +5024,7 @@
       </c>
       <c r="N4" s="92">
         <f>+N2*N3</f>
-        <v>486948</v>
+        <v>4869480</v>
       </c>
       <c r="O4" s="91"/>
     </row>
@@ -5056,7 +5056,7 @@
       </c>
       <c r="N7" s="92">
         <f>+N4-N5+N6</f>
-        <v>492087</v>
+        <v>4874619</v>
       </c>
     </row>
   </sheetData>
@@ -5684,31 +5684,31 @@
       <c r="Q14" s="128"/>
       <c r="R14" s="128"/>
       <c r="S14" s="128">
-        <f>SUM(S9:S12)</f>
+        <f t="shared" ref="S14:Y14" si="0">SUM(S9:S12)</f>
         <v>9370.4399999999987</v>
       </c>
       <c r="T14" s="128">
-        <f>SUM(T9:T12)</f>
+        <f t="shared" si="0"/>
         <v>9559.3100000000013</v>
       </c>
       <c r="U14" s="128">
-        <f>SUM(U9:U12)</f>
+        <f t="shared" si="0"/>
         <v>9824.7029999999995</v>
       </c>
       <c r="V14" s="128">
-        <f>SUM(V9:V12)</f>
+        <f t="shared" si="0"/>
         <v>10246.512999999999</v>
       </c>
       <c r="W14" s="128">
-        <f>SUM(W9:W12)</f>
+        <f t="shared" si="0"/>
         <v>10542.800999999999</v>
       </c>
       <c r="X14" s="128">
-        <f>SUM(X9:X12)</f>
+        <f t="shared" si="0"/>
         <v>11079.166000000001</v>
       </c>
       <c r="Y14" s="128">
-        <f>SUM(Y9:Y12)</f>
+        <f t="shared" si="0"/>
         <v>11510.307000000001</v>
       </c>
       <c r="Z14" s="128">
@@ -5807,11 +5807,11 @@
         <f>SUM(G15:J15)</f>
         <v>17332.683000000001</v>
       </c>
-      <c r="AH15" s="137">
+      <c r="AH15" s="77">
         <f>SUM(S15:V15)</f>
         <v>21038.464</v>
       </c>
-      <c r="AI15" s="137">
+      <c r="AI15" s="77">
         <f>SUM(W15:Z15)</f>
         <v>22762.287874499998</v>
       </c>
@@ -5821,19 +5821,19 @@
         <v>113</v>
       </c>
       <c r="C16" s="76">
-        <f t="shared" ref="C16" si="0">C14-C15</f>
+        <f t="shared" ref="C16" si="1">C14-C15</f>
         <v>2167.9899999999998</v>
       </c>
       <c r="D16" s="76">
-        <f t="shared" ref="D16" si="1">D14-D15</f>
+        <f t="shared" ref="D16" si="2">D14-D15</f>
         <v>2504.5790000000002</v>
       </c>
       <c r="E16" s="76">
-        <f t="shared" ref="E16" si="2">E14-E15</f>
+        <f t="shared" ref="E16" si="3">E14-E15</f>
         <v>2567.8859999999995</v>
       </c>
       <c r="F16" s="76">
-        <f t="shared" ref="F16" si="3">F14-F15</f>
+        <f t="shared" ref="F16" si="4">F14-F15</f>
         <v>2479.2820000000002</v>
       </c>
       <c r="G16" s="76">
@@ -5845,7 +5845,7 @@
         <v>3323.7690000000002</v>
       </c>
       <c r="I16" s="76">
-        <f t="shared" ref="G16:J16" si="4">I14-I15</f>
+        <f t="shared" ref="I16" si="5">I14-I15</f>
         <v>3276.8779999999997</v>
       </c>
       <c r="J16" s="76">
@@ -5864,31 +5864,31 @@
       <c r="Q16" s="76"/>
       <c r="R16" s="76"/>
       <c r="S16" s="76">
-        <f>+S14-S15</f>
+        <f t="shared" ref="S16:Y16" si="6">+S14-S15</f>
         <v>4393.3669999999984</v>
       </c>
       <c r="T16" s="76">
-        <f>+T14-T15</f>
+        <f t="shared" si="6"/>
         <v>4385.1670000000013</v>
       </c>
       <c r="U16" s="76">
-        <f>+U14-U15</f>
+        <f t="shared" si="6"/>
         <v>4704.8189999999995</v>
       </c>
       <c r="V16" s="76">
-        <f>+V14-V15</f>
+        <f t="shared" si="6"/>
         <v>4479.1489999999994</v>
       </c>
       <c r="W16" s="76">
-        <f>+W14-W15</f>
+        <f t="shared" si="6"/>
         <v>5279.6539999999995</v>
       </c>
       <c r="X16" s="76">
-        <f>+X14-X15</f>
+        <f t="shared" si="6"/>
         <v>5753.8550000000014</v>
       </c>
       <c r="Y16" s="76">
-        <f>+Y14-Y15</f>
+        <f t="shared" si="6"/>
         <v>5346.0570000000007</v>
       </c>
       <c r="Z16" s="76">
@@ -5981,11 +5981,11 @@
         <f>SUM(G17:J17)</f>
         <v>2545.1459999999997</v>
       </c>
-      <c r="AH17" s="137">
+      <c r="AH17" s="77">
         <f>SUM(S17:V17)</f>
         <v>2917.5540000000001</v>
       </c>
-      <c r="AI17" s="137">
+      <c r="AI17" s="77">
         <f>SUM(W17:Z17)</f>
         <v>3164.134</v>
       </c>
@@ -6063,11 +6063,11 @@
         <f>SUM(G18:J18)</f>
         <v>2273.8850000000002</v>
       </c>
-      <c r="AH18" s="137">
+      <c r="AH18" s="77">
         <f>SUM(S18:V18)</f>
         <v>2925.2950000000001</v>
       </c>
-      <c r="AI18" s="137">
+      <c r="AI18" s="77">
         <f>SUM(W18:Z18)</f>
         <v>3277.5949999999998</v>
       </c>
@@ -6145,11 +6145,11 @@
         <f>SUM(G19:J19)</f>
         <v>1351.6210000000001</v>
       </c>
-      <c r="AH19" s="137">
+      <c r="AH19" s="77">
         <f>SUM(S19:V19)</f>
         <v>1702.039</v>
       </c>
-      <c r="AI19" s="137">
+      <c r="AI19" s="77">
         <f>SUM(W19:Z19)</f>
         <v>1774.28</v>
       </c>
@@ -6159,7 +6159,7 @@
         <v>114</v>
       </c>
       <c r="C20" s="84">
-        <f t="shared" ref="C20:J20" si="5">SUM(C17:C19)</f>
+        <f t="shared" ref="C20:E20" si="7">SUM(C17:C19)</f>
         <v>1209.7339999999999</v>
       </c>
       <c r="D20" s="84">
@@ -6167,31 +6167,31 @@
         <v>1146.6509999999998</v>
       </c>
       <c r="E20" s="84">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>1253.0230000000001</v>
       </c>
       <c r="F20" s="84">
-        <f>SUM(F17:F19)</f>
+        <f t="shared" ref="F20:K20" si="8">SUM(F17:F19)</f>
         <v>1525.04</v>
       </c>
       <c r="G20" s="84">
-        <f>SUM(G17:G19)</f>
+        <f t="shared" si="8"/>
         <v>1334.915</v>
       </c>
       <c r="H20" s="84">
-        <f>SUM(H17:H19)</f>
+        <f t="shared" si="8"/>
         <v>1476.1389999999999</v>
       </c>
       <c r="I20" s="84">
-        <f>SUM(I17:I19)</f>
+        <f t="shared" si="8"/>
         <v>1521.625</v>
       </c>
       <c r="J20" s="84">
-        <f>SUM(J17:J19)</f>
+        <f t="shared" si="8"/>
         <v>1837.973</v>
       </c>
       <c r="K20" s="84">
-        <f>SUM(K17:K19)</f>
+        <f t="shared" si="8"/>
         <v>1611.4359999999997</v>
       </c>
       <c r="L20" s="84"/>
@@ -6206,31 +6206,31 @@
         <v>1760.8330000000001</v>
       </c>
       <c r="T20" s="84">
-        <f t="shared" ref="T20:Z20" si="6">+T19+T18+T17</f>
+        <f t="shared" ref="T20:Z20" si="9">+T19+T18+T17</f>
         <v>1782.33</v>
       </c>
       <c r="U20" s="84">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v>1795.3420000000001</v>
       </c>
       <c r="V20" s="84">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v>2206.3829999999998</v>
       </c>
       <c r="W20" s="84">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v>1932.6549999999997</v>
       </c>
       <c r="X20" s="84">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v>1979.1610000000001</v>
       </c>
       <c r="Y20" s="84">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v>2097.81</v>
       </c>
       <c r="Z20" s="84">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v>2206.3829999999998</v>
       </c>
       <c r="AA20" s="84"/>
@@ -6255,15 +6255,15 @@
         <v>958.25599999999986</v>
       </c>
       <c r="D21" s="84">
-        <f t="shared" ref="D21:K21" si="7">D16-D20</f>
+        <f t="shared" ref="D21:I21" si="10">D16-D20</f>
         <v>1357.9280000000003</v>
       </c>
       <c r="E21" s="84">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>1314.8629999999994</v>
       </c>
       <c r="F21" s="84">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>954.24200000000019</v>
       </c>
       <c r="G21" s="84">
@@ -6271,11 +6271,11 @@
         <v>1959.8560000000002</v>
       </c>
       <c r="H21" s="84">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>1847.6300000000003</v>
       </c>
       <c r="I21" s="84">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>1755.2529999999997</v>
       </c>
       <c r="J21" s="84">
@@ -6298,27 +6298,27 @@
         <v>2632.5339999999983</v>
       </c>
       <c r="T21" s="84">
-        <f t="shared" ref="T21:Z21" si="8">+T16-T20</f>
+        <f t="shared" ref="T21:Y21" si="11">+T16-T20</f>
         <v>2602.8370000000014</v>
       </c>
       <c r="U21" s="84">
-        <f t="shared" si="8"/>
+        <f t="shared" si="11"/>
         <v>2909.4769999999994</v>
       </c>
       <c r="V21" s="84">
-        <f t="shared" si="8"/>
+        <f t="shared" si="11"/>
         <v>2272.7659999999996</v>
       </c>
       <c r="W21" s="84">
-        <f t="shared" si="8"/>
+        <f t="shared" si="11"/>
         <v>3346.9989999999998</v>
       </c>
       <c r="X21" s="84">
-        <f t="shared" si="8"/>
+        <f t="shared" si="11"/>
         <v>3774.6940000000013</v>
       </c>
       <c r="Y21" s="84">
-        <f t="shared" si="8"/>
+        <f t="shared" si="11"/>
         <v>3248.2470000000008</v>
       </c>
       <c r="Z21" s="84">
@@ -6419,11 +6419,11 @@
         <f>SUM(G22:J22)</f>
         <v>-765.62</v>
       </c>
-      <c r="AH22" s="137">
+      <c r="AH22" s="77">
         <f>SUM(S22:V22)</f>
         <v>-451.95699999999999</v>
       </c>
-      <c r="AI22" s="137">
+      <c r="AI22" s="77">
         <f>SUM(W22:Z22)</f>
         <v>-553.96600000000001</v>
       </c>
@@ -6488,7 +6488,7 @@
         <v>98</v>
       </c>
       <c r="C24" s="84">
-        <f t="shared" ref="C24:K24" si="9">SUM(C20:C23)</f>
+        <f t="shared" ref="C24:J24" si="12">SUM(C20:C23)</f>
         <v>2005.6039999999996</v>
       </c>
       <c r="D24" s="84">
@@ -6496,27 +6496,27 @@
         <v>2182.2530000000002</v>
       </c>
       <c r="E24" s="84">
-        <f t="shared" si="9"/>
+        <f t="shared" si="12"/>
         <v>2114.4829999999993</v>
       </c>
       <c r="F24" s="84">
-        <f t="shared" si="9"/>
+        <f t="shared" si="12"/>
         <v>2031.4569999999999</v>
       </c>
       <c r="G24" s="84">
-        <f t="shared" si="9"/>
+        <f t="shared" si="12"/>
         <v>3369.4170000000004</v>
       </c>
       <c r="H24" s="84">
-        <f t="shared" si="9"/>
+        <f t="shared" si="12"/>
         <v>3069.9280000000003</v>
       </c>
       <c r="I24" s="84">
-        <f t="shared" si="9"/>
+        <f t="shared" si="12"/>
         <v>3182.5839999999998</v>
       </c>
       <c r="J24" s="84">
-        <f t="shared" si="9"/>
+        <f t="shared" si="12"/>
         <v>2388.8260000000005</v>
       </c>
       <c r="K24" s="84">
@@ -6535,27 +6535,27 @@
         <v>2614.5789999999984</v>
       </c>
       <c r="T24" s="84">
-        <f t="shared" ref="T24:Z24" si="10">+T21+T22</f>
+        <f t="shared" ref="T24:Y24" si="13">+T21+T22</f>
         <v>2513.8560000000016</v>
       </c>
       <c r="U24" s="84">
-        <f t="shared" si="10"/>
+        <f t="shared" si="13"/>
         <v>2702.9539999999993</v>
       </c>
       <c r="V24" s="84">
-        <f t="shared" si="10"/>
+        <f t="shared" si="13"/>
         <v>2134.2679999999996</v>
       </c>
       <c r="W24" s="84">
-        <f t="shared" si="10"/>
+        <f t="shared" si="13"/>
         <v>3213.7259999999997</v>
       </c>
       <c r="X24" s="84">
-        <f t="shared" si="10"/>
+        <f t="shared" si="13"/>
         <v>3631.6750000000011</v>
       </c>
       <c r="Y24" s="84">
-        <f t="shared" si="10"/>
+        <f t="shared" si="13"/>
         <v>3109.4100000000008</v>
       </c>
       <c r="Z24" s="84">
@@ -6654,11 +6654,11 @@
         <f>SUM(G25:J25)</f>
         <v>-723.875</v>
       </c>
-      <c r="AH25" s="137">
+      <c r="AH25" s="77">
         <f>SUM(S25:V25)</f>
         <v>1254.0260000000001</v>
       </c>
-      <c r="AI25" s="137">
+      <c r="AI25" s="77">
         <f>SUM(W25:Z25)</f>
         <v>1906.4345113249997</v>
       </c>
@@ -6672,35 +6672,35 @@
         <v>1918.8009999999995</v>
       </c>
       <c r="D26" s="85">
-        <f t="shared" ref="D26:F26" si="11">D24+D25</f>
+        <f t="shared" ref="D26:F26" si="14">D24+D25</f>
         <v>1866.8470000000002</v>
       </c>
       <c r="E26" s="85">
-        <f t="shared" si="11"/>
+        <f t="shared" si="14"/>
         <v>2042.9989999999993</v>
       </c>
       <c r="F26" s="85">
-        <f t="shared" si="11"/>
+        <f t="shared" si="14"/>
         <v>2067.1959999999999</v>
       </c>
       <c r="G26" s="85">
-        <f t="shared" ref="G26:K26" si="12">G24+G25</f>
+        <f t="shared" ref="G26:K26" si="15">G24+G25</f>
         <v>3041.6300000000006</v>
       </c>
       <c r="H26" s="85">
-        <f t="shared" si="12"/>
+        <f t="shared" si="15"/>
         <v>2829.1520000000005</v>
       </c>
       <c r="I26" s="85">
-        <f t="shared" si="12"/>
+        <f t="shared" si="15"/>
         <v>2970.6959999999999</v>
       </c>
       <c r="J26" s="85">
-        <f t="shared" si="12"/>
+        <f t="shared" si="15"/>
         <v>2445.4020000000005</v>
       </c>
       <c r="K26" s="85">
-        <f t="shared" si="12"/>
+        <f t="shared" si="15"/>
         <v>3208.8829999999998</v>
       </c>
       <c r="L26" s="85"/>
@@ -6715,27 +6715,27 @@
         <v>2332.2089999999985</v>
       </c>
       <c r="T26" s="84">
-        <f t="shared" ref="T26:Z26" si="13">+T24-T25</f>
+        <f t="shared" ref="T26:Y26" si="16">+T24-T25</f>
         <v>2147.3060000000014</v>
       </c>
       <c r="U26" s="84">
-        <f t="shared" si="13"/>
+        <f t="shared" si="16"/>
         <v>2363.5089999999991</v>
       </c>
       <c r="V26" s="84">
-        <f t="shared" si="13"/>
+        <f t="shared" si="16"/>
         <v>1868.6069999999995</v>
       </c>
       <c r="W26" s="84">
-        <f t="shared" si="13"/>
+        <f t="shared" si="16"/>
         <v>2890.3509999999997</v>
       </c>
       <c r="X26" s="84">
-        <f t="shared" si="13"/>
+        <f t="shared" si="16"/>
         <v>3125.4130000000009</v>
       </c>
       <c r="Y26" s="84">
-        <f t="shared" si="13"/>
+        <f t="shared" si="16"/>
         <v>2546.9160000000006</v>
       </c>
       <c r="Z26" s="84">
@@ -6801,27 +6801,27 @@
       <c r="Q27" s="85"/>
       <c r="R27" s="85"/>
       <c r="S27" s="86">
-        <f t="shared" ref="S27:X27" si="14">+S26/S28</f>
+        <f t="shared" ref="S27:X27" si="17">+S26/S28</f>
         <v>5.2806246518768054</v>
       </c>
       <c r="T27" s="86">
-        <f t="shared" si="14"/>
+        <f t="shared" si="17"/>
         <v>4.8831374974700941</v>
       </c>
       <c r="U27" s="86">
-        <f t="shared" si="14"/>
+        <f t="shared" si="17"/>
         <v>5.3973961972879509</v>
       </c>
       <c r="V27" s="86">
-        <f t="shared" si="14"/>
+        <f t="shared" si="17"/>
         <v>4.2683114581096691</v>
       </c>
       <c r="W27" s="86">
-        <f t="shared" si="14"/>
+        <f t="shared" si="17"/>
         <v>6.6146507018916969</v>
       </c>
       <c r="X27" s="86">
-        <f t="shared" si="14"/>
+        <f t="shared" si="17"/>
         <v>7.186790470080461</v>
       </c>
       <c r="Y27" s="86">
@@ -6840,11 +6840,11 @@
       <c r="AE27" s="86">
         <v>11.55</v>
       </c>
-      <c r="AH27" s="138">
+      <c r="AH27" s="130">
         <f>+AH26/AH28</f>
         <v>19.832098422550633</v>
       </c>
-      <c r="AI27" s="138">
+      <c r="AI27" s="130">
         <f>+AI26/AI28</f>
         <v>26.385228689258092</v>
       </c>
@@ -7053,19 +7053,19 @@
       </c>
       <c r="F32" s="122"/>
       <c r="G32" s="122">
-        <f t="shared" ref="G32:J32" si="15">G14/C14-1</f>
+        <f t="shared" ref="G32:J32" si="18">G14/C14-1</f>
         <v>0.24196701938436038</v>
       </c>
       <c r="H32" s="122">
-        <f t="shared" si="15"/>
+        <f t="shared" si="18"/>
         <v>0.1941176776747211</v>
       </c>
       <c r="I32" s="122">
-        <f t="shared" si="15"/>
+        <f t="shared" si="18"/>
         <v>0.16281682761162575</v>
       </c>
       <c r="J32" s="122">
-        <f t="shared" si="15"/>
+        <f t="shared" si="18"/>
         <v>0.16026567768971423</v>
       </c>
       <c r="K32" s="122">
@@ -7077,15 +7077,15 @@
         <v>0.12511269481475806</v>
       </c>
       <c r="X32" s="122">
-        <f t="shared" ref="X32:Z32" si="16">+X14/T14-1</f>
+        <f t="shared" ref="X32:Z32" si="19">+X14/T14-1</f>
         <v>0.15899222851858541</v>
       </c>
       <c r="Y32" s="122">
-        <f t="shared" si="16"/>
+        <f t="shared" si="19"/>
         <v>0.17156793442000251</v>
       </c>
       <c r="Z32" s="122">
-        <f t="shared" si="16"/>
+        <f t="shared" si="19"/>
         <v>0.14999999999999991</v>
       </c>
     </row>
@@ -7098,7 +7098,7 @@
         <v>6.7434345185634736E-2</v>
       </c>
       <c r="L33" s="122">
-        <f t="shared" ref="L33" si="17">L3/H3-1</f>
+        <f t="shared" ref="L33" si="20">L3/H3-1</f>
         <v>5.000478057175628E-2</v>
       </c>
       <c r="M33" s="122"/>
@@ -7677,27 +7677,27 @@
         <v>2332.2089999999985</v>
       </c>
       <c r="T52" s="84">
-        <f t="shared" ref="T52:Y52" si="18">+T26</f>
+        <f t="shared" ref="T52:Y52" si="21">+T26</f>
         <v>2147.3060000000014</v>
       </c>
       <c r="U52" s="84">
-        <f t="shared" si="18"/>
+        <f t="shared" si="21"/>
         <v>2363.5089999999991</v>
       </c>
       <c r="V52" s="84">
-        <f t="shared" si="18"/>
+        <f t="shared" si="21"/>
         <v>1868.6069999999995</v>
       </c>
       <c r="W52" s="84">
-        <f t="shared" si="18"/>
+        <f t="shared" si="21"/>
         <v>2890.3509999999997</v>
       </c>
       <c r="X52" s="84">
-        <f t="shared" si="18"/>
+        <f t="shared" si="21"/>
         <v>3125.4130000000009</v>
       </c>
       <c r="Y52" s="84">
-        <f t="shared" si="18"/>
+        <f t="shared" si="21"/>
         <v>2546.9160000000006</v>
       </c>
     </row>
@@ -7965,15 +7965,15 @@
         <v>1536.8939999999998</v>
       </c>
       <c r="W62" s="84">
-        <f t="shared" ref="W62:Y62" si="19">SUM(W53:W61)</f>
+        <f t="shared" ref="W62:Y62" si="22">SUM(W53:W61)</f>
         <v>2789.1990000000001</v>
       </c>
       <c r="X62" s="84">
-        <f t="shared" si="19"/>
+        <f t="shared" si="22"/>
         <v>2423.2579999999998</v>
       </c>
       <c r="Y62" s="84">
-        <f t="shared" si="19"/>
+        <f t="shared" si="22"/>
         <v>2825.174</v>
       </c>
     </row>
@@ -8065,27 +8065,27 @@
         <v>-75.713999999999999</v>
       </c>
       <c r="T67" s="84">
-        <f t="shared" ref="T67:Y67" si="20">+T64+T65+T66</f>
+        <f t="shared" ref="T67:Y67" si="23">+T64+T65+T66</f>
         <v>-78.287000000000006</v>
       </c>
       <c r="U67" s="84">
-        <f t="shared" si="20"/>
+        <f t="shared" si="23"/>
         <v>-1869.1090000000002</v>
       </c>
       <c r="V67" s="84">
-        <f t="shared" si="20"/>
+        <f t="shared" si="23"/>
         <v>-158.67400000000001</v>
       </c>
       <c r="W67" s="84">
-        <f t="shared" si="20"/>
+        <f t="shared" si="23"/>
         <v>485.66199999999998</v>
       </c>
       <c r="X67" s="84">
-        <f t="shared" si="20"/>
+        <f t="shared" si="23"/>
         <v>768.68399999999997</v>
       </c>
       <c r="Y67" s="84">
-        <f t="shared" si="20"/>
+        <f t="shared" si="23"/>
         <v>43.871000000000009</v>
       </c>
     </row>
@@ -8180,31 +8180,31 @@
         <v>158</v>
       </c>
       <c r="S72" s="84">
-        <f>SUM(S69:S71)</f>
+        <f t="shared" ref="S72:Y72" si="24">SUM(S69:S71)</f>
         <v>-2132.9440000000004</v>
       </c>
       <c r="T72" s="84">
-        <f>SUM(T69:T71)</f>
+        <f t="shared" si="24"/>
         <v>-1489.3810000000001</v>
       </c>
       <c r="U72" s="84">
-        <f>SUM(U69:U71)</f>
+        <f t="shared" si="24"/>
         <v>226.59600000000006</v>
       </c>
       <c r="V72" s="84">
-        <f>SUM(V69:V71)</f>
+        <f t="shared" si="24"/>
         <v>-678.69800000000009</v>
       </c>
       <c r="W72" s="84">
-        <f>SUM(W69:W71)</f>
+        <f t="shared" si="24"/>
         <v>-4028.3160000000003</v>
       </c>
       <c r="X72" s="84">
-        <f>SUM(X69:X71)</f>
+        <f t="shared" si="24"/>
         <v>-2502.8679999999999</v>
       </c>
       <c r="Y72" s="84">
-        <f>SUM(Y69:Y71)</f>
+        <f t="shared" si="24"/>
         <v>-1737.029</v>
       </c>
     </row>
@@ -8213,31 +8213,31 @@
         <v>159</v>
       </c>
       <c r="S73" s="84">
-        <f>+S72+S67+S62</f>
+        <f t="shared" ref="S73:Y73" si="25">+S72+S67+S62</f>
         <v>3.8639999999991232</v>
       </c>
       <c r="T73" s="84">
-        <f>+T72+T67+T62</f>
+        <f t="shared" si="25"/>
         <v>-276.82099999999991</v>
       </c>
       <c r="U73" s="84">
-        <f>+U72+U67+U62</f>
+        <f t="shared" si="25"/>
         <v>678.58800000000042</v>
       </c>
       <c r="V73" s="84">
-        <f>+V72+V67+V62</f>
+        <f t="shared" si="25"/>
         <v>699.52199999999971</v>
       </c>
       <c r="W73" s="84">
-        <f>+W72+W67+W62</f>
+        <f t="shared" si="25"/>
         <v>-753.45500000000038</v>
       </c>
       <c r="X73" s="84">
-        <f>+X72+X67+X62</f>
+        <f t="shared" si="25"/>
         <v>689.07399999999984</v>
       </c>
       <c r="Y73" s="84">
-        <f>+Y72+Y67+Y62</f>
+        <f t="shared" si="25"/>
         <v>1132.0160000000001</v>
       </c>
     </row>
@@ -9621,18 +9621,18 @@
     <row r="5" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="95"/>
       <c r="B5" s="72"/>
-      <c r="C5" s="130" t="s">
+      <c r="C5" s="131" t="s">
         <v>38</v>
       </c>
-      <c r="D5" s="130"/>
-      <c r="E5" s="130"/>
-      <c r="F5" s="130"/>
-      <c r="G5" s="131" t="s">
+      <c r="D5" s="131"/>
+      <c r="E5" s="131"/>
+      <c r="F5" s="131"/>
+      <c r="G5" s="132" t="s">
         <v>38</v>
       </c>
-      <c r="H5" s="131"/>
-      <c r="I5" s="131"/>
-      <c r="J5" s="131"/>
+      <c r="H5" s="132"/>
+      <c r="I5" s="132"/>
+      <c r="J5" s="132"/>
       <c r="K5" s="99" t="s">
         <v>33</v>
       </c>
@@ -12033,14 +12033,14 @@
       <c r="D3" s="38"/>
     </row>
     <row r="4" spans="1:19" s="32" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="133" t="s">
+      <c r="A4" s="134" t="s">
         <v>79</v>
       </c>
-      <c r="B4" s="134"/>
-      <c r="C4" s="134"/>
-      <c r="D4" s="134"/>
-      <c r="E4" s="134"/>
-      <c r="F4" s="134"/>
+      <c r="B4" s="135"/>
+      <c r="C4" s="135"/>
+      <c r="D4" s="135"/>
+      <c r="E4" s="135"/>
+      <c r="F4" s="135"/>
     </row>
     <row r="5" spans="1:19" s="32" customFormat="1" ht="33.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="19"/>
@@ -12048,21 +12048,21 @@
       <c r="C5" s="19"/>
       <c r="D5" s="19"/>
       <c r="F5" s="46"/>
-      <c r="G5" s="135" t="s">
+      <c r="G5" s="136" t="s">
         <v>32</v>
       </c>
-      <c r="H5" s="135"/>
-      <c r="I5" s="135"/>
-      <c r="J5" s="135"/>
+      <c r="H5" s="136"/>
+      <c r="I5" s="136"/>
+      <c r="J5" s="136"/>
       <c r="K5" s="47" t="s">
         <v>57</v>
       </c>
-      <c r="L5" s="132" t="s">
+      <c r="L5" s="133" t="s">
         <v>32</v>
       </c>
-      <c r="M5" s="132"/>
-      <c r="N5" s="132"/>
-      <c r="O5" s="132"/>
+      <c r="M5" s="133"/>
+      <c r="N5" s="133"/>
+      <c r="O5" s="133"/>
       <c r="P5" s="47" t="s">
         <v>57</v>
       </c>
@@ -13492,58 +13492,58 @@
     </row>
     <row r="45" spans="1:19" ht="26.15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A45" s="25"/>
-      <c r="F45" s="136" t="s">
+      <c r="F45" s="137" t="s">
         <v>86</v>
       </c>
-      <c r="G45" s="136"/>
-      <c r="H45" s="136"/>
-      <c r="I45" s="136"/>
-      <c r="J45" s="136"/>
-      <c r="K45" s="136"/>
-      <c r="L45" s="136"/>
-      <c r="M45" s="136"/>
-      <c r="N45" s="136"/>
-      <c r="O45" s="136"/>
-      <c r="P45" s="136"/>
-      <c r="Q45" s="136"/>
+      <c r="G45" s="137"/>
+      <c r="H45" s="137"/>
+      <c r="I45" s="137"/>
+      <c r="J45" s="137"/>
+      <c r="K45" s="137"/>
+      <c r="L45" s="137"/>
+      <c r="M45" s="137"/>
+      <c r="N45" s="137"/>
+      <c r="O45" s="137"/>
+      <c r="P45" s="137"/>
+      <c r="Q45" s="137"/>
       <c r="R45" s="62"/>
       <c r="S45" s="62"/>
     </row>
     <row r="46" spans="1:19" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A46" s="25"/>
-      <c r="F46" s="136" t="s">
+      <c r="F46" s="137" t="s">
         <v>84</v>
       </c>
-      <c r="G46" s="136"/>
-      <c r="H46" s="136"/>
-      <c r="I46" s="136"/>
-      <c r="J46" s="136"/>
-      <c r="K46" s="136"/>
-      <c r="L46" s="136"/>
-      <c r="M46" s="136"/>
-      <c r="N46" s="136"/>
-      <c r="O46" s="136"/>
-      <c r="P46" s="136"/>
-      <c r="Q46" s="136"/>
+      <c r="G46" s="137"/>
+      <c r="H46" s="137"/>
+      <c r="I46" s="137"/>
+      <c r="J46" s="137"/>
+      <c r="K46" s="137"/>
+      <c r="L46" s="137"/>
+      <c r="M46" s="137"/>
+      <c r="N46" s="137"/>
+      <c r="O46" s="137"/>
+      <c r="P46" s="137"/>
+      <c r="Q46" s="137"/>
       <c r="R46" s="62"/>
       <c r="S46" s="62"/>
     </row>
     <row r="47" spans="1:19" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B47" s="26"/>
-      <c r="F47" s="136" t="s">
+      <c r="F47" s="137" t="s">
         <v>82</v>
       </c>
-      <c r="G47" s="136"/>
-      <c r="H47" s="136"/>
-      <c r="I47" s="136"/>
-      <c r="J47" s="136"/>
-      <c r="K47" s="136"/>
-      <c r="L47" s="136"/>
-      <c r="M47" s="136"/>
-      <c r="N47" s="136"/>
-      <c r="O47" s="136"/>
-      <c r="P47" s="136"/>
-      <c r="Q47" s="136"/>
+      <c r="G47" s="137"/>
+      <c r="H47" s="137"/>
+      <c r="I47" s="137"/>
+      <c r="J47" s="137"/>
+      <c r="K47" s="137"/>
+      <c r="L47" s="137"/>
+      <c r="M47" s="137"/>
+      <c r="N47" s="137"/>
+      <c r="O47" s="137"/>
+      <c r="P47" s="137"/>
+      <c r="Q47" s="137"/>
       <c r="R47" s="62"/>
       <c r="S47" s="62"/>
     </row>
